--- a/coupon-uat/references/UAT คูปองส่วนลด TA(BOTH).xlsx
+++ b/coupon-uat/references/UAT คูปองส่วนลด TA(BOTH).xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="คู่มือคำนวณส่วนลด" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -475,13 +475,13 @@
     <t>ฐาน = เบี้ยเท่านั้น; ตรวจ Min Purchase จากฐานนี้; ส่วนลด = MIN(เบี้ย × %, Max Discount)</t>
   </si>
   <si>
-    <t>ฐาน = เบี้ยเท่านั้น; ตรวจ Min Purchase จากฐานนี้; ส่วนลด = MIN(Fix Amount, เบี้ยรวม)</t>
+    <t>ฐาน = เบี้ยเท่านั้น; ตรวจ Min Purchase จากยอดเต็ม (เบี้ย + VAT + Duty); ส่วนลด = MIN(Fix Amount, เบี้ยรวม)</t>
   </si>
   <si>
     <t>Min Purchase</t>
   </si>
   <si>
-    <t>ถ้าฐานรวมต่ำกว่า Min Purchase → ส่วนลดทั้งหมดเป็น 0</t>
+    <t>ตัวที่ใช้ตรวจ Min Purchase: Fix Amount / % Include VAT = เบี้ย + VAT + Duty, % Exclude VAT = เบี้ย — ถ้าต่ำกว่า Min Purchase ส่วนลดทั้งหมดเป็น 0</t>
   </si>
   <si>
     <t>Test Case</t>
@@ -2068,7 +2068,7 @@
       <c r="J5" s="45"/>
       <c r="K5" s="45"/>
       <c r="L5" s="46">
-        <f t="shared" ref="L5:L10" si="2">IF(F5="","",IF(OR(J5="",(R5+IF(F5=2,AA5,0))&gt;=J5),IF(AND(D5="Percentage",ISNUMBER(K5)),MIN(IF(D5="Fix Amount",MIN(MAX(0,H5),MAX(0,(R5+IF(F5=2,AA5,0)))),MIN(MAX(0,(R5+IF(F5=2,AA5,0))*H5/100),MAX(0,(R5+IF(F5=2,AA5,0))))),MAX(0,K5)),IF(D5="Fix Amount",MIN(MAX(0,H5),MAX(0,(R5+IF(F5=2,AA5,0)))),MIN(MAX(0,(R5+IF(F5=2,AA5,0))*H5/100),MAX(0,(R5+IF(F5=2,AA5,0)))))),0))</f>
+        <f t="shared" ref="L5:L10" si="2">IF(F5="","",IF(OR(J5="",IF(D5="Fix Amount",Q5+IF(F5=2,Z5,0),R5+IF(F5=2,AA5,0))&gt;=J5),IF(AND(D5="Percentage",ISNUMBER(K5)),MIN(IF(D5="Fix Amount",MIN(MAX(0,H5),MAX(0,(R5+IF(F5=2,AA5,0)))),MIN(MAX(0,(R5+IF(F5=2,AA5,0))*H5/100),MAX(0,(R5+IF(F5=2,AA5,0))))),MAX(0,K5)),IF(D5="Fix Amount",MIN(MAX(0,H5),MAX(0,(R5+IF(F5=2,AA5,0)))),MIN(MAX(0,(R5+IF(F5=2,AA5,0))*H5/100),MAX(0,(R5+IF(F5=2,AA5,0)))))),0))</f>
         <v>50</v>
       </c>
       <c r="M5" s="46">
@@ -3049,7 +3049,7 @@
       <c r="J12" s="55"/>
       <c r="K12" s="55"/>
       <c r="L12" s="56">
-        <f t="shared" ref="L12:L17" si="33">IF(F12="","",IF(OR(J12="",(R12+IF(F12=2,AA12,0))&gt;=J12),IF(AND(D12="Percentage",ISNUMBER(K12)),MIN(IF(D12="Fix Amount",MIN(MAX(0,H12),MAX(0,(R12+IF(F12=2,AA12,0)))),MIN(MAX(0,(R12+IF(F12=2,AA12,0))*H12/100),MAX(0,(R12+IF(F12=2,AA12,0))))),MAX(0,K12)),IF(D12="Fix Amount",MIN(MAX(0,H12),MAX(0,(R12+IF(F12=2,AA12,0)))),MIN(MAX(0,(R12+IF(F12=2,AA12,0))*H12/100),MAX(0,(R12+IF(F12=2,AA12,0)))))),0))</f>
+        <f t="shared" ref="L12:L17" si="33">IF(F12="","",IF(OR(J12="",IF(D12="Fix Amount",Q12+IF(F12=2,Z12,0),R12+IF(F12=2,AA12,0))&gt;=J12),IF(AND(D12="Percentage",ISNUMBER(K12)),MIN(IF(D12="Fix Amount",MIN(MAX(0,H12),MAX(0,(R12+IF(F12=2,AA12,0)))),MIN(MAX(0,(R12+IF(F12=2,AA12,0))*H12/100),MAX(0,(R12+IF(F12=2,AA12,0))))),MAX(0,K12)),IF(D12="Fix Amount",MIN(MAX(0,H12),MAX(0,(R12+IF(F12=2,AA12,0)))),MIN(MAX(0,(R12+IF(F12=2,AA12,0))*H12/100),MAX(0,(R12+IF(F12=2,AA12,0)))))),0))</f>
         <v>10</v>
       </c>
       <c r="M12" s="56">
@@ -4050,7 +4050,7 @@
       <c r="J19" s="45"/>
       <c r="K19" s="45"/>
       <c r="L19" s="46">
-        <f t="shared" ref="L19:L24" si="60">IF(F19="","",IF(OR(J19="",(R19+IF(F19=2,AA19,0))&gt;=J19),IF(AND(D19="Percentage",ISNUMBER(K19)),MIN(IF(D19="Fix Amount",MIN(MAX(0,H19),MAX(0,(R19+IF(F19=2,AA19,0)))),MIN(MAX(0,(R19+IF(F19=2,AA19,0))*H19/100),MAX(0,(R19+IF(F19=2,AA19,0))))),MAX(0,K19)),IF(D19="Fix Amount",MIN(MAX(0,H19),MAX(0,(R19+IF(F19=2,AA19,0)))),MIN(MAX(0,(R19+IF(F19=2,AA19,0))*H19/100),MAX(0,(R19+IF(F19=2,AA19,0)))))),0))</f>
+        <f t="shared" ref="L19:L24" si="60">IF(F19="","",IF(OR(J19="",IF(D19="Fix Amount",Q19+IF(F19=2,Z19,0),R19+IF(F19=2,AA19,0))&gt;=J19),IF(AND(D19="Percentage",ISNUMBER(K19)),MIN(IF(D19="Fix Amount",MIN(MAX(0,H19),MAX(0,(R19+IF(F19=2,AA19,0)))),MIN(MAX(0,(R19+IF(F19=2,AA19,0))*H19/100),MAX(0,(R19+IF(F19=2,AA19,0))))),MAX(0,K19)),IF(D19="Fix Amount",MIN(MAX(0,H19),MAX(0,(R19+IF(F19=2,AA19,0)))),MIN(MAX(0,(R19+IF(F19=2,AA19,0))*H19/100),MAX(0,(R19+IF(F19=2,AA19,0)))))),0))</f>
         <v>50</v>
       </c>
       <c r="M19" s="46">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="K28" s="59"/>
       <c r="L28" s="56">
-        <f t="shared" ref="L28:L997" si="92">IF(F28="","",IF(OR(J28="",(R28+IF(F28=2,AA28,0))&gt;=J28),IF(AND(D28="Percentage",ISNUMBER(K28)),MIN(IF(D28="Fix Amount",MIN(MAX(0,H28),MAX(0,(R28+IF(F28=2,AA28,0)))),MIN(MAX(0,(R28+IF(F28=2,AA28,0))*H28/100),MAX(0,(R28+IF(F28=2,AA28,0))))),MAX(0,K28)),IF(D28="Fix Amount",MIN(MAX(0,H28),MAX(0,(R28+IF(F28=2,AA28,0)))),MIN(MAX(0,(R28+IF(F28=2,AA28,0))*H28/100),MAX(0,(R28+IF(F28=2,AA28,0)))))),0))</f>
+        <f t="shared" ref="L28:L997" si="92">IF(F28="","",IF(OR(J28="",IF(D28="Fix Amount",Q28+IF(F28=2,Z28,0),R28+IF(F28=2,AA28,0))&gt;=J28),IF(AND(D28="Percentage",ISNUMBER(K28)),MIN(IF(D28="Fix Amount",MIN(MAX(0,H28),MAX(0,(R28+IF(F28=2,AA28,0)))),MIN(MAX(0,(R28+IF(F28=2,AA28,0))*H28/100),MAX(0,(R28+IF(F28=2,AA28,0))))),MAX(0,K28)),IF(D28="Fix Amount",MIN(MAX(0,H28),MAX(0,(R28+IF(F28=2,AA28,0)))),MIN(MAX(0,(R28+IF(F28=2,AA28,0))*H28/100),MAX(0,(R28+IF(F28=2,AA28,0)))))),0))</f>
         <v>30</v>
       </c>
       <c r="M28" s="56">
@@ -5790,16 +5790,36 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="61"/>
-      <c r="B32" s="60"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
+      <c r="A32" s="61">
+        <v>23</v>
+      </c>
+      <c r="B32" s="60">
+        <v>318</v>
+      </c>
+      <c r="C32" s="61" t="inlineStr">
+        <is>
+          <t>Min Purchase ตัวอย่าง A: Fix Amount ได้รับส่วนลด (เบี้ย 80 + VAT 10 + Duty 10 = 100 ≥ Min 100)</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="61">
+        <v>1</v>
+      </c>
+      <c r="G32" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="H32" s="61">
+        <v>20</v>
+      </c>
       <c r="I32" s="61"/>
-      <c r="J32" s="68"/>
+      <c r="J32" s="68">
+        <v>100</v>
+      </c>
       <c r="K32" s="68"/>
       <c r="L32" s="54" t="str">
         <f t="shared" si="92"/>
@@ -5809,9 +5829,15 @@
         <f t="shared" si="93"/>
         <v/>
       </c>
-      <c r="N32" s="61"/>
-      <c r="O32" s="61"/>
-      <c r="P32" s="61"/>
+      <c r="N32" s="61">
+        <v>80</v>
+      </c>
+      <c r="O32" s="61">
+        <v>10</v>
+      </c>
+      <c r="P32" s="61">
+        <v>10</v>
+      </c>
       <c r="Q32" s="61"/>
       <c r="R32" s="61"/>
       <c r="S32" s="61"/>
@@ -5861,16 +5887,36 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="61"/>
-      <c r="B33" s="60"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
+      <c r="A33" s="61">
+        <v>24</v>
+      </c>
+      <c r="B33" s="60">
+        <v>319</v>
+      </c>
+      <c r="C33" s="61" t="inlineStr">
+        <is>
+          <t>Min Purchase ตัวอย่าง B: Percentage Include VAT ได้รับส่วนลด (ยอดเต็ม 100 ≥ Min 100)</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F33" s="61">
+        <v>1</v>
+      </c>
+      <c r="G33" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="H33" s="61">
+        <v>10</v>
+      </c>
       <c r="I33" s="61"/>
-      <c r="J33" s="68"/>
+      <c r="J33" s="68">
+        <v>100</v>
+      </c>
       <c r="K33" s="68"/>
       <c r="L33" s="54" t="str">
         <f t="shared" si="92"/>
@@ -5880,9 +5926,15 @@
         <f t="shared" si="93"/>
         <v/>
       </c>
-      <c r="N33" s="61"/>
-      <c r="O33" s="61"/>
-      <c r="P33" s="61"/>
+      <c r="N33" s="61">
+        <v>80</v>
+      </c>
+      <c r="O33" s="61">
+        <v>10</v>
+      </c>
+      <c r="P33" s="61">
+        <v>10</v>
+      </c>
       <c r="Q33" s="69"/>
       <c r="R33" s="61"/>
       <c r="S33" s="61"/>
@@ -5932,16 +5984,36 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="61"/>
-      <c r="B34" s="60"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
+      <c r="A34" s="61">
+        <v>25</v>
+      </c>
+      <c r="B34" s="60">
+        <v>319</v>
+      </c>
+      <c r="C34" s="61" t="inlineStr">
+        <is>
+          <t>Min Purchase ตัวอย่าง C: Percentage Exclude VAT ไม่ได้รับส่วนลด (เบี้ย 80 &lt; Min 100)</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" s="61">
+        <v>1</v>
+      </c>
+      <c r="G34" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="H34" s="61">
+        <v>20</v>
+      </c>
       <c r="I34" s="61"/>
-      <c r="J34" s="68"/>
+      <c r="J34" s="68">
+        <v>100</v>
+      </c>
       <c r="K34" s="68"/>
       <c r="L34" s="54" t="str">
         <f t="shared" si="92"/>
@@ -5951,9 +6023,15 @@
         <f t="shared" si="93"/>
         <v/>
       </c>
-      <c r="N34" s="61"/>
-      <c r="O34" s="61"/>
-      <c r="P34" s="61"/>
+      <c r="N34" s="61">
+        <v>80</v>
+      </c>
+      <c r="O34" s="61">
+        <v>10</v>
+      </c>
+      <c r="P34" s="61">
+        <v>10</v>
+      </c>
       <c r="Q34" s="69"/>
       <c r="R34" s="61"/>
       <c r="S34" s="61"/>
